--- a/sources/table_normalization/xlsx/economy-table27.xlsx
+++ b/sources/table_normalization/xlsx/economy-table27.xlsx
@@ -567,16 +567,16 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -6493,71 +6493,11 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B60:H60"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B88:H88"/>
-    <mergeCell ref="B89:H89"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="B91:H91"/>
-    <mergeCell ref="B101:H101"/>
-    <mergeCell ref="B102:H102"/>
-    <mergeCell ref="B103:H103"/>
-    <mergeCell ref="B104:H104"/>
-    <mergeCell ref="B114:H114"/>
-    <mergeCell ref="B115:H115"/>
-    <mergeCell ref="B116:H116"/>
-    <mergeCell ref="B117:H117"/>
-    <mergeCell ref="B119:H119"/>
-    <mergeCell ref="B120:H120"/>
-    <mergeCell ref="B121:H121"/>
-    <mergeCell ref="B122:H122"/>
-    <mergeCell ref="B124:H124"/>
-    <mergeCell ref="B125:H125"/>
-    <mergeCell ref="B126:H126"/>
-    <mergeCell ref="B127:H127"/>
-    <mergeCell ref="B129:H129"/>
-    <mergeCell ref="B130:H130"/>
-    <mergeCell ref="B131:H131"/>
-    <mergeCell ref="B132:H132"/>
-    <mergeCell ref="B142:H142"/>
-    <mergeCell ref="B143:H143"/>
-    <mergeCell ref="B144:H144"/>
-    <mergeCell ref="B145:H145"/>
-    <mergeCell ref="B155:H155"/>
-    <mergeCell ref="B156:H156"/>
-    <mergeCell ref="B157:H157"/>
-    <mergeCell ref="B158:H158"/>
-    <mergeCell ref="B168:H168"/>
-    <mergeCell ref="B169:H169"/>
-    <mergeCell ref="B170:H170"/>
-    <mergeCell ref="B171:H171"/>
-    <mergeCell ref="B181:H181"/>
-    <mergeCell ref="B182:H182"/>
-    <mergeCell ref="B183:H183"/>
-    <mergeCell ref="B184:H184"/>
-    <mergeCell ref="B194:H194"/>
-    <mergeCell ref="B195:H195"/>
-    <mergeCell ref="B196:H196"/>
-    <mergeCell ref="B197:H197"/>
-    <mergeCell ref="B207:H207"/>
-    <mergeCell ref="B208:H208"/>
-    <mergeCell ref="B209:H209"/>
-    <mergeCell ref="B210:H210"/>
+    <mergeCell ref="I168:I171"/>
+    <mergeCell ref="I181:I184"/>
+    <mergeCell ref="I194:I197"/>
+    <mergeCell ref="I207:I210"/>
+    <mergeCell ref="I232:I235"/>
     <mergeCell ref="B232:H232"/>
     <mergeCell ref="B233:H233"/>
     <mergeCell ref="B234:H234"/>
@@ -6574,11 +6514,71 @@
     <mergeCell ref="I129:I132"/>
     <mergeCell ref="I142:I145"/>
     <mergeCell ref="I155:I158"/>
-    <mergeCell ref="I168:I171"/>
-    <mergeCell ref="I181:I184"/>
-    <mergeCell ref="I194:I197"/>
-    <mergeCell ref="I207:I210"/>
-    <mergeCell ref="I232:I235"/>
+    <mergeCell ref="B197:H197"/>
+    <mergeCell ref="B207:H207"/>
+    <mergeCell ref="B208:H208"/>
+    <mergeCell ref="B209:H209"/>
+    <mergeCell ref="B210:H210"/>
+    <mergeCell ref="B183:H183"/>
+    <mergeCell ref="B184:H184"/>
+    <mergeCell ref="B194:H194"/>
+    <mergeCell ref="B195:H195"/>
+    <mergeCell ref="B196:H196"/>
+    <mergeCell ref="B169:H169"/>
+    <mergeCell ref="B170:H170"/>
+    <mergeCell ref="B171:H171"/>
+    <mergeCell ref="B181:H181"/>
+    <mergeCell ref="B182:H182"/>
+    <mergeCell ref="B155:H155"/>
+    <mergeCell ref="B156:H156"/>
+    <mergeCell ref="B157:H157"/>
+    <mergeCell ref="B158:H158"/>
+    <mergeCell ref="B168:H168"/>
+    <mergeCell ref="B132:H132"/>
+    <mergeCell ref="B142:H142"/>
+    <mergeCell ref="B143:H143"/>
+    <mergeCell ref="B144:H144"/>
+    <mergeCell ref="B145:H145"/>
+    <mergeCell ref="B126:H126"/>
+    <mergeCell ref="B127:H127"/>
+    <mergeCell ref="B129:H129"/>
+    <mergeCell ref="B130:H130"/>
+    <mergeCell ref="B131:H131"/>
+    <mergeCell ref="B120:H120"/>
+    <mergeCell ref="B121:H121"/>
+    <mergeCell ref="B122:H122"/>
+    <mergeCell ref="B124:H124"/>
+    <mergeCell ref="B125:H125"/>
+    <mergeCell ref="B114:H114"/>
+    <mergeCell ref="B115:H115"/>
+    <mergeCell ref="B116:H116"/>
+    <mergeCell ref="B117:H117"/>
+    <mergeCell ref="B119:H119"/>
+    <mergeCell ref="B91:H91"/>
+    <mergeCell ref="B101:H101"/>
+    <mergeCell ref="B102:H102"/>
+    <mergeCell ref="B103:H103"/>
+    <mergeCell ref="B104:H104"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B262" r:id="rId1"/>
